--- a/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_event.xlsx
+++ b/files/scripts/statistical_test_scripts/rq3_result/rq3_pairwise_wilcoxon_event.xlsx
@@ -2848,30 +2848,26 @@
         <v>100</v>
       </c>
       <c r="G47" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H47" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I47" t="n">
         <v>0</v>
       </c>
       <c r="J47" t="n">
+        <v>1.476775219335459e-67</v>
+      </c>
+      <c r="K47" t="n">
         <v>1</v>
       </c>
-      <c r="K47" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M47" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
@@ -2901,30 +2897,26 @@
         <v>100</v>
       </c>
       <c r="G48" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H48" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I48" t="n">
         <v>0</v>
       </c>
       <c r="J48" t="n">
+        <v>1.476775219335459e-67</v>
+      </c>
+      <c r="K48" t="n">
         <v>1</v>
       </c>
-      <c r="K48" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
@@ -2954,30 +2946,26 @@
         <v>100</v>
       </c>
       <c r="G49" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="H49" t="n">
-        <v>0</v>
+        <v>10.34</v>
       </c>
       <c r="I49" t="n">
         <v>0</v>
       </c>
       <c r="J49" t="n">
+        <v>1.476775219335459e-67</v>
+      </c>
+      <c r="K49" t="n">
         <v>1</v>
       </c>
-      <c r="K49" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M49" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
@@ -3163,33 +3151,29 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G53" t="n">
         <v>100</v>
       </c>
       <c r="H53" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I53" t="n">
         <v>0</v>
       </c>
       <c r="J53" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K53" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
@@ -3216,33 +3200,29 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G54" t="n">
         <v>100</v>
       </c>
       <c r="H54" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I54" t="n">
         <v>0</v>
       </c>
       <c r="J54" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K54" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
@@ -3269,33 +3249,29 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>100</v>
+        <v>89.66</v>
       </c>
       <c r="G55" t="n">
         <v>100</v>
       </c>
       <c r="H55" t="n">
-        <v>0</v>
+        <v>-10.34</v>
       </c>
       <c r="I55" t="n">
         <v>0</v>
       </c>
       <c r="J55" t="n">
-        <v>1</v>
+        <v>1.476775219335459e-67</v>
       </c>
       <c r="K55" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M55" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
@@ -3374,30 +3350,26 @@
         <v>100</v>
       </c>
       <c r="G57" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="H57" t="n">
-        <v>0</v>
+        <v>83.87</v>
       </c>
       <c r="I57" t="n">
         <v>0</v>
       </c>
       <c r="J57" t="n">
+        <v>2.332500941489082e-67</v>
+      </c>
+      <c r="K57" t="n">
         <v>1</v>
       </c>
-      <c r="K57" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M57" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
@@ -3427,30 +3399,26 @@
         <v>100</v>
       </c>
       <c r="G58" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="H58" t="n">
-        <v>0</v>
+        <v>80.75</v>
       </c>
       <c r="I58" t="n">
         <v>0</v>
       </c>
       <c r="J58" t="n">
+        <v>2.387238385100547e-67</v>
+      </c>
+      <c r="K58" t="n">
         <v>1</v>
       </c>
-      <c r="K58" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M58" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
@@ -3480,30 +3448,26 @@
         <v>100</v>
       </c>
       <c r="G59" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H59" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K59" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L59" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
@@ -3533,30 +3497,26 @@
         <v>100</v>
       </c>
       <c r="G60" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H60" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K60" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L60" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M60" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
@@ -3586,30 +3546,26 @@
         <v>100</v>
       </c>
       <c r="G61" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H61" t="n">
-        <v>0</v>
+        <v>3.435000000000002</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>1</v>
+        <v>8.345820413725095e-61</v>
       </c>
       <c r="K61" t="n">
-        <v>0.5</v>
+        <v>0.95</v>
       </c>
       <c r="L61" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M61" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
@@ -3639,10 +3595,10 @@
         <v>8.56</v>
       </c>
       <c r="G62" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H62" t="n">
-        <v>-91.44</v>
+        <v>-87.7</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
@@ -3685,33 +3641,29 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>100</v>
+        <v>16.13</v>
       </c>
       <c r="G63" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H63" t="n">
-        <v>0</v>
+        <v>-79.69</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K63" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L63" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M63" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
@@ -3738,33 +3690,29 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>100</v>
+        <v>19.25</v>
       </c>
       <c r="G64" t="n">
-        <v>100</v>
+        <v>96.565</v>
       </c>
       <c r="H64" t="n">
-        <v>0</v>
+        <v>-76.03999999999999</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>1</v>
+        <v>2.387238385100547e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M64" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
@@ -3803,10 +3751,10 @@
         <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K65" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -3852,10 +3800,10 @@
         <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K66" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -3901,10 +3849,10 @@
         <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K67" t="n">
-        <v>0.9086538461538461</v>
+        <v>1</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -3941,30 +3889,26 @@
         <v>100</v>
       </c>
       <c r="G68" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H68" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I68" t="n">
         <v>0</v>
       </c>
       <c r="J68" t="n">
+        <v>3.878578144017659e-72</v>
+      </c>
+      <c r="K68" t="n">
         <v>1</v>
       </c>
-      <c r="K68" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L68" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M68" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
@@ -3994,30 +3938,26 @@
         <v>100</v>
       </c>
       <c r="G69" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H69" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I69" t="n">
         <v>0</v>
       </c>
       <c r="J69" t="n">
+        <v>3.878578144017659e-72</v>
+      </c>
+      <c r="K69" t="n">
         <v>1</v>
       </c>
-      <c r="K69" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L69" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M69" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
@@ -4047,30 +3987,26 @@
         <v>100</v>
       </c>
       <c r="G70" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H70" t="n">
-        <v>0</v>
+        <v>3.329999999999998</v>
       </c>
       <c r="I70" t="n">
         <v>0</v>
       </c>
       <c r="J70" t="n">
+        <v>3.878578144017659e-72</v>
+      </c>
+      <c r="K70" t="n">
         <v>1</v>
       </c>
-      <c r="K70" t="n">
-        <v>0.5</v>
-      </c>
       <c r="L70" t="inlineStr">
         <is>
-          <t>negligible</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>all ties</t>
-        </is>
-      </c>
+          <t>large</t>
+        </is>
+      </c>
+      <c r="M70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
@@ -4100,19 +4036,19 @@
         <v>33.33</v>
       </c>
       <c r="G71" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H71" t="n">
-        <v>-66.67</v>
+        <v>-63.34</v>
       </c>
       <c r="I71" t="n">
         <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K71" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -4149,19 +4085,19 @@
         <v>35</v>
       </c>
       <c r="G72" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H72" t="n">
-        <v>-65</v>
+        <v>-61.67</v>
       </c>
       <c r="I72" t="n">
         <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K72" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -4198,19 +4134,19 @@
         <v>36.67</v>
       </c>
       <c r="G73" t="n">
-        <v>100</v>
+        <v>96.67</v>
       </c>
       <c r="H73" t="n">
-        <v>-63.33</v>
+        <v>-60</v>
       </c>
       <c r="I73" t="n">
         <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>2.603243595271822e-59</v>
+        <v>4.033339917615288e-71</v>
       </c>
       <c r="K73" t="n">
-        <v>0.09134615384615384</v>
+        <v>0</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
@@ -4343,7 +4279,7 @@
         <v>47.725</v>
       </c>
       <c r="G2" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="H2" t="n">
         <v>20.445</v>
@@ -4401,10 +4337,10 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.001953125</v>
+        <v>0.0009765625</v>
       </c>
       <c r="K3" t="n">
-        <v>0.8819444444444444</v>
+        <v>0.9166666666666666</v>
       </c>
       <c r="L3" t="inlineStr">
         <is>
@@ -4447,13 +4383,13 @@
         <v>8.329999999999998</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J4" t="n">
         <v>0.03125</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7013888888888888</v>
+        <v>0.6875</v>
       </c>
       <c r="L4" t="inlineStr">
         <is>
@@ -4634,13 +4570,13 @@
         <v>12</v>
       </c>
       <c r="F8" t="n">
-        <v>27.78</v>
+        <v>26.935</v>
       </c>
       <c r="G8" t="n">
         <v>57.14</v>
       </c>
       <c r="H8" t="n">
-        <v>-28.105</v>
+        <v>-30.64</v>
       </c>
       <c r="I8" t="n">
         <v>0</v>
@@ -4689,7 +4625,7 @@
         <v>57.14</v>
       </c>
       <c r="H9" t="n">
-        <v>-25.435</v>
+        <v>-21.965</v>
       </c>
       <c r="I9" t="n">
         <v>0</v>
@@ -4698,7 +4634,7 @@
         <v>0.0009765625</v>
       </c>
       <c r="K9" t="n">
-        <v>0.06944444444444445</v>
+        <v>0.04513888888888889</v>
       </c>
       <c r="L9" t="inlineStr">
         <is>
@@ -4738,16 +4674,16 @@
         <v>57.14</v>
       </c>
       <c r="H10" t="n">
-        <v>-15.745</v>
+        <v>-12.175</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.015625</v>
+        <v>0.03125</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2222222222222222</v>
+        <v>0.2361111111111111</v>
       </c>
       <c r="L10" t="inlineStr">
         <is>
@@ -4882,19 +4818,19 @@
         <v>13.57</v>
       </c>
       <c r="G13" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="H13" t="n">
-        <v>-0.5800000000000001</v>
+        <v>-0.5600000000000005</v>
       </c>
       <c r="I13" t="n">
-        <v>133</v>
+        <v>126</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8932116031646729</v>
+        <v>0.7313888072967529</v>
       </c>
       <c r="K13" t="n">
-        <v>0.4914933837429111</v>
+        <v>0.5066162570888468</v>
       </c>
       <c r="L13" t="inlineStr">
         <is>
@@ -5173,7 +5109,7 @@
         <v>23</v>
       </c>
       <c r="F19" t="n">
-        <v>13.64</v>
+        <v>13.33</v>
       </c>
       <c r="G19" t="n">
         <v>13.64</v>
@@ -5182,17 +5118,17 @@
         <v>-0.9499999999999993</v>
       </c>
       <c r="I19" t="n">
-        <v>124.5</v>
+        <v>122</v>
       </c>
       <c r="J19" t="n">
-        <v>0.9482252929562537</v>
+        <v>0.8838460571465129</v>
       </c>
       <c r="K19" t="n">
-        <v>0.44234404536862</v>
+        <v>0.4196597353497165</v>
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M19" t="inlineStr"/>
@@ -5228,16 +5164,16 @@
         <v>12.24</v>
       </c>
       <c r="H20" t="n">
-        <v>5.52</v>
+        <v>5.550000000000001</v>
       </c>
       <c r="I20" t="n">
-        <v>14</v>
+        <v>39</v>
       </c>
       <c r="J20" t="n">
-        <v>4.471124253338281e-08</v>
+        <v>2.487789406985899e-07</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9438775510204082</v>
+        <v>0.9563492063492064</v>
       </c>
       <c r="L20" t="inlineStr">
         <is>
@@ -5274,19 +5210,19 @@
         <v>7.35</v>
       </c>
       <c r="G21" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="H21" t="n">
-        <v>2.02</v>
+        <v>2.319999999999999</v>
       </c>
       <c r="I21" t="n">
-        <v>89</v>
+        <v>78.5</v>
       </c>
       <c r="J21" t="n">
-        <v>5.804848178000667e-06</v>
+        <v>3.090184895751452e-06</v>
       </c>
       <c r="K21" t="n">
-        <v>0.7590702947845805</v>
+        <v>0.7619047619047619</v>
       </c>
       <c r="L21" t="inlineStr">
         <is>
@@ -5323,19 +5259,19 @@
         <v>5.73</v>
       </c>
       <c r="G22" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="H22" t="n">
         <v>2.085</v>
       </c>
       <c r="I22" t="n">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="J22" t="n">
-        <v>1.325261405577772e-06</v>
+        <v>1.41254233028078e-06</v>
       </c>
       <c r="K22" t="n">
-        <v>0.7301587301587301</v>
+        <v>0.7278911564625851</v>
       </c>
       <c r="L22" t="inlineStr">
         <is>
@@ -5522,13 +5458,13 @@
         <v>5.585</v>
       </c>
       <c r="H26" t="n">
-        <v>7.5975</v>
+        <v>7.265000000000001</v>
       </c>
       <c r="I26" t="n">
         <v>0</v>
       </c>
       <c r="J26" t="n">
-        <v>1.647408099309982e-08</v>
+        <v>4.547473508864641e-13</v>
       </c>
       <c r="K26" t="n">
         <v>1</v>
@@ -5565,22 +5501,22 @@
         <v>42</v>
       </c>
       <c r="F27" t="n">
-        <v>4.58</v>
+        <v>4.455</v>
       </c>
       <c r="G27" t="n">
         <v>5.585</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.2324999999999993</v>
+        <v>-0.1925000000000001</v>
       </c>
       <c r="I27" t="n">
-        <v>441.5</v>
+        <v>422</v>
       </c>
       <c r="J27" t="n">
-        <v>0.9004926110924971</v>
+        <v>0.7122227637754117</v>
       </c>
       <c r="K27" t="n">
-        <v>0.4744897959183674</v>
+        <v>0.4682539682539683</v>
       </c>
       <c r="L27" t="inlineStr">
         <is>
@@ -5614,7 +5550,7 @@
         <v>42</v>
       </c>
       <c r="F28" t="n">
-        <v>3.56</v>
+        <v>3.7</v>
       </c>
       <c r="G28" t="n">
         <v>5.585</v>
@@ -5623,13 +5559,13 @@
         <v>-1.6</v>
       </c>
       <c r="I28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="J28" t="n">
-        <v>9.818973152847362e-07</v>
+        <v>8.643826460024959e-07</v>
       </c>
       <c r="K28" t="n">
-        <v>0.2607709750566893</v>
+        <v>0.2653061224489796</v>
       </c>
       <c r="L28" t="inlineStr">
         <is>
@@ -5666,19 +5602,19 @@
         <v>37.905</v>
       </c>
       <c r="G29" t="n">
-        <v>31.48</v>
+        <v>31.465</v>
       </c>
       <c r="H29" t="n">
         <v>7.310000000000002</v>
       </c>
       <c r="I29" t="n">
-        <v>27700.5</v>
+        <v>26904.5</v>
       </c>
       <c r="J29" t="n">
-        <v>8.709978202486797e-27</v>
+        <v>5.809087336959167e-28</v>
       </c>
       <c r="K29" t="n">
-        <v>0.759532104320898</v>
+        <v>0.7640501766100547</v>
       </c>
       <c r="L29" t="inlineStr">
         <is>
@@ -5715,19 +5651,19 @@
         <v>41.85</v>
       </c>
       <c r="G30" t="n">
-        <v>34.33</v>
+        <v>34.48</v>
       </c>
       <c r="H30" t="n">
         <v>10</v>
       </c>
       <c r="I30" t="n">
-        <v>24793</v>
+        <v>24983</v>
       </c>
       <c r="J30" t="n">
-        <v>3.286373001545587e-31</v>
+        <v>6.55506525850639e-31</v>
       </c>
       <c r="K30" t="n">
-        <v>0.7410001451589491</v>
+        <v>0.7407763584458316</v>
       </c>
       <c r="L30" t="inlineStr">
         <is>
@@ -5764,19 +5700,19 @@
         <v>51.21</v>
       </c>
       <c r="G31" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="H31" t="n">
-        <v>13.1</v>
+        <v>13.11</v>
       </c>
       <c r="I31" t="n">
-        <v>10741.5</v>
+        <v>10652.5</v>
       </c>
       <c r="J31" t="n">
-        <v>1.532316504167253e-56</v>
+        <v>6.098914174881242e-57</v>
       </c>
       <c r="K31" t="n">
-        <v>0.8061765132820439</v>
+        <v>0.8070172255286205</v>
       </c>
       <c r="L31" t="inlineStr">
         <is>
@@ -5957,22 +5893,22 @@
         <v>498</v>
       </c>
       <c r="F35" t="n">
-        <v>31.48</v>
+        <v>31.465</v>
       </c>
       <c r="G35" t="n">
         <v>43.92</v>
       </c>
       <c r="H35" t="n">
-        <v>-13.385</v>
+        <v>-13.58</v>
       </c>
       <c r="I35" t="n">
-        <v>4546</v>
+        <v>4161.5</v>
       </c>
       <c r="J35" t="n">
-        <v>8.089763848075026e-72</v>
+        <v>9.344317594485901e-73</v>
       </c>
       <c r="K35" t="n">
-        <v>0.1041535620393219</v>
+        <v>0.1015588458250673</v>
       </c>
       <c r="L35" t="inlineStr">
         <is>
@@ -6006,22 +5942,22 @@
         <v>498</v>
       </c>
       <c r="F36" t="n">
-        <v>34.33</v>
+        <v>34.48</v>
       </c>
       <c r="G36" t="n">
         <v>43.92</v>
       </c>
       <c r="H36" t="n">
-        <v>-11.64</v>
+        <v>-11.51</v>
       </c>
       <c r="I36" t="n">
-        <v>7243.5</v>
+        <v>7453.5</v>
       </c>
       <c r="J36" t="n">
-        <v>2.041387191104076e-65</v>
+        <v>6.244837326614357e-65</v>
       </c>
       <c r="K36" t="n">
-        <v>0.1772027870518217</v>
+        <v>0.177489072756891</v>
       </c>
       <c r="L36" t="inlineStr">
         <is>
@@ -6055,22 +5991,22 @@
         <v>498</v>
       </c>
       <c r="F37" t="n">
-        <v>38.04</v>
+        <v>38.02</v>
       </c>
       <c r="G37" t="n">
         <v>43.92</v>
       </c>
       <c r="H37" t="n">
-        <v>-7.669999999999998</v>
+        <v>-7.922499999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>6934</v>
+        <v>6719</v>
       </c>
       <c r="J37" t="n">
-        <v>4.091547268298832e-54</v>
+        <v>7.260753727435013e-55</v>
       </c>
       <c r="K37" t="n">
-        <v>0.2859187755036209</v>
+        <v>0.2833905904743472</v>
       </c>
       <c r="L37" t="inlineStr">
         <is>
@@ -6104,22 +6040,22 @@
         <v>2664</v>
       </c>
       <c r="F38" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="G38" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="H38" t="n">
-        <v>-4.040000000000003</v>
+        <v>-3.995000000000001</v>
       </c>
       <c r="I38" t="n">
-        <v>324953.5</v>
+        <v>320848.5</v>
       </c>
       <c r="J38" t="n">
-        <v>1.44440270717659e-291</v>
+        <v>2.040466348060846e-293</v>
       </c>
       <c r="K38" t="n">
-        <v>0.2051196748550352</v>
+        <v>0.2047766375609844</v>
       </c>
       <c r="L38" t="inlineStr">
         <is>
@@ -6153,22 +6089,22 @@
         <v>2664</v>
       </c>
       <c r="F39" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="G39" t="n">
-        <v>18.475</v>
+        <v>18.415</v>
       </c>
       <c r="H39" t="n">
-        <v>-5.42</v>
+        <v>-5.469999999999999</v>
       </c>
       <c r="I39" t="n">
-        <v>41344.5</v>
+        <v>46171</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
       </c>
       <c r="K39" t="n">
-        <v>0.1192856003526049</v>
+        <v>0.1193077227001777</v>
       </c>
       <c r="L39" t="inlineStr">
         <is>
@@ -6202,22 +6138,22 @@
         <v>2664</v>
       </c>
       <c r="F40" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G40" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="H40" t="n">
         <v>-5.04</v>
       </c>
       <c r="I40" t="n">
-        <v>36004.5</v>
+        <v>36448</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
       </c>
       <c r="K40" t="n">
-        <v>0.1015446753059366</v>
+        <v>0.1013201405234063</v>
       </c>
       <c r="L40" t="inlineStr">
         <is>
@@ -6251,22 +6187,22 @@
         <v>2664</v>
       </c>
       <c r="F41" t="n">
-        <v>23.68</v>
+        <v>23.695</v>
       </c>
       <c r="G41" t="n">
         <v>15.18</v>
       </c>
       <c r="H41" t="n">
-        <v>8.065000000000001</v>
+        <v>8.119999999999997</v>
       </c>
       <c r="I41" t="n">
-        <v>3779.5</v>
+        <v>3793.5</v>
       </c>
       <c r="J41" t="n">
         <v>0</v>
       </c>
       <c r="K41" t="n">
-        <v>0.9734703030733436</v>
+        <v>0.9742189402240078</v>
       </c>
       <c r="L41" t="inlineStr">
         <is>
@@ -6300,22 +6236,22 @@
         <v>2664</v>
       </c>
       <c r="F42" t="n">
-        <v>13.235</v>
+        <v>13.205</v>
       </c>
       <c r="G42" t="n">
         <v>15.18</v>
       </c>
       <c r="H42" t="n">
-        <v>-2.167499999999999</v>
+        <v>-2.2075</v>
       </c>
       <c r="I42" t="n">
-        <v>562118.5</v>
+        <v>561952</v>
       </c>
       <c r="J42" t="n">
-        <v>1.769125809693663e-204</v>
+        <v>9.436502711524469e-205</v>
       </c>
       <c r="K42" t="n">
-        <v>0.2816849084444805</v>
+        <v>0.2794259631252874</v>
       </c>
       <c r="L42" t="inlineStr">
         <is>
@@ -6349,22 +6285,22 @@
         <v>2664</v>
       </c>
       <c r="F43" t="n">
-        <v>8.949999999999999</v>
+        <v>8.94</v>
       </c>
       <c r="G43" t="n">
         <v>15.18</v>
       </c>
       <c r="H43" t="n">
-        <v>-6.1475</v>
+        <v>-6.162500000000001</v>
       </c>
       <c r="I43" t="n">
-        <v>61872.5</v>
+        <v>61823</v>
       </c>
       <c r="J43" t="n">
         <v>0</v>
       </c>
       <c r="K43" t="n">
-        <v>0.07464798695091487</v>
+        <v>0.07469991105970836</v>
       </c>
       <c r="L43" t="inlineStr">
         <is>
@@ -6398,22 +6334,22 @@
         <v>2664</v>
       </c>
       <c r="F44" t="n">
-        <v>27.54</v>
+        <v>27.52</v>
       </c>
       <c r="G44" t="n">
         <v>15.18</v>
       </c>
       <c r="H44" t="n">
-        <v>12.18</v>
+        <v>12.21</v>
       </c>
       <c r="I44" t="n">
-        <v>5246</v>
+        <v>5978</v>
       </c>
       <c r="J44" t="n">
         <v>0</v>
       </c>
       <c r="K44" t="n">
-        <v>0.9889362194401609</v>
+        <v>0.9888106011416822</v>
       </c>
       <c r="L44" t="inlineStr">
         <is>
@@ -6447,22 +6383,22 @@
         <v>2664</v>
       </c>
       <c r="F45" t="n">
-        <v>18.475</v>
+        <v>18.415</v>
       </c>
       <c r="G45" t="n">
         <v>15.18</v>
       </c>
       <c r="H45" t="n">
-        <v>2.999999999999997</v>
+        <v>2.972499999999998</v>
       </c>
       <c r="I45" t="n">
-        <v>214269</v>
+        <v>221480</v>
       </c>
       <c r="J45" t="n">
         <v>0</v>
       </c>
       <c r="K45" t="n">
-        <v>0.7468862443524605</v>
+        <v>0.7454499826402979</v>
       </c>
       <c r="L45" t="inlineStr">
         <is>
@@ -6496,7 +6432,7 @@
         <v>2664</v>
       </c>
       <c r="F46" t="n">
-        <v>13.87</v>
+        <v>13.89</v>
       </c>
       <c r="G46" t="n">
         <v>15.18</v>
@@ -6505,13 +6441,13 @@
         <v>-1.015</v>
       </c>
       <c r="I46" t="n">
-        <v>1156183.5</v>
+        <v>1162986</v>
       </c>
       <c r="J46" t="n">
-        <v>9.495243422859468e-55</v>
+        <v>1.365829814466042e-53</v>
       </c>
       <c r="K46" t="n">
-        <v>0.3932728477351225</v>
+        <v>0.3936790816717619</v>
       </c>
       <c r="L46" t="inlineStr">
         <is>
@@ -6545,26 +6481,26 @@
         <v>400</v>
       </c>
       <c r="F47" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="G47" t="n">
-        <v>3.92</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="H47" t="n">
-        <v>3.495</v>
+        <v>0.8499999999999996</v>
       </c>
       <c r="I47" t="n">
-        <v>13187.5</v>
+        <v>34231</v>
       </c>
       <c r="J47" t="n">
-        <v>4.692968315310286e-31</v>
+        <v>0.01119012136909999</v>
       </c>
       <c r="K47" t="n">
-        <v>0.750921875</v>
+        <v>0.52550625</v>
       </c>
       <c r="L47" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="M47" t="inlineStr"/>
@@ -6594,26 +6530,26 @@
         <v>400</v>
       </c>
       <c r="F48" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G48" t="n">
-        <v>3.55</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="H48" t="n">
-        <v>2.160000000000001</v>
+        <v>0.07000000000000028</v>
       </c>
       <c r="I48" t="n">
-        <v>15421.5</v>
+        <v>32677.5</v>
       </c>
       <c r="J48" t="n">
-        <v>3.985380047889337e-26</v>
+        <v>0.002225582370063115</v>
       </c>
       <c r="K48" t="n">
-        <v>0.688846875</v>
+        <v>0.473159375</v>
       </c>
       <c r="L48" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="M48" t="inlineStr"/>
@@ -6643,26 +6579,26 @@
         <v>400</v>
       </c>
       <c r="F49" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G49" t="n">
-        <v>2.71</v>
+        <v>4.225</v>
       </c>
       <c r="H49" t="n">
-        <v>2.54</v>
+        <v>0.7650000000000001</v>
       </c>
       <c r="I49" t="n">
-        <v>8465</v>
+        <v>37650</v>
       </c>
       <c r="J49" t="n">
-        <v>1.028016353348811e-41</v>
+        <v>0.4682672276534862</v>
       </c>
       <c r="K49" t="n">
-        <v>0.730034375</v>
+        <v>0.521909375</v>
       </c>
       <c r="L49" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="M49" t="inlineStr"/>
@@ -6692,22 +6628,22 @@
         <v>400</v>
       </c>
       <c r="F50" t="n">
-        <v>9.18</v>
+        <v>9.43</v>
       </c>
       <c r="G50" t="n">
         <v>4.91</v>
       </c>
       <c r="H50" t="n">
-        <v>3.779999999999999</v>
+        <v>3.7875</v>
       </c>
       <c r="I50" t="n">
-        <v>6381</v>
+        <v>0</v>
       </c>
       <c r="J50" t="n">
-        <v>4.780935321319239e-45</v>
+        <v>2.358504551631038e-64</v>
       </c>
       <c r="K50" t="n">
-        <v>0.710940625</v>
+        <v>0.760303125</v>
       </c>
       <c r="L50" t="inlineStr">
         <is>
@@ -6741,22 +6677,22 @@
         <v>400</v>
       </c>
       <c r="F51" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G51" t="n">
         <v>4.91</v>
       </c>
       <c r="H51" t="n">
-        <v>1.395</v>
+        <v>1.420000000000001</v>
       </c>
       <c r="I51" t="n">
-        <v>12232</v>
+        <v>4790</v>
       </c>
       <c r="J51" t="n">
-        <v>3.911097176705411e-30</v>
+        <v>4.806020455855334e-49</v>
       </c>
       <c r="K51" t="n">
-        <v>0.5660375</v>
+        <v>0.60566875</v>
       </c>
       <c r="L51" t="inlineStr">
         <is>
@@ -6790,26 +6726,26 @@
         <v>400</v>
       </c>
       <c r="F52" t="n">
-        <v>6.84</v>
+        <v>6.94</v>
       </c>
       <c r="G52" t="n">
         <v>4.91</v>
       </c>
       <c r="H52" t="n">
-        <v>1.39</v>
+        <v>1.405</v>
       </c>
       <c r="I52" t="n">
-        <v>16397.5</v>
+        <v>9704.5</v>
       </c>
       <c r="J52" t="n">
-        <v>2.112800801416368e-21</v>
+        <v>1.507075686974922e-35</v>
       </c>
       <c r="K52" t="n">
-        <v>0.53355625</v>
+        <v>0.57093125</v>
       </c>
       <c r="L52" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>small</t>
         </is>
       </c>
       <c r="M52" t="inlineStr"/>
@@ -6839,26 +6775,26 @@
         <v>400</v>
       </c>
       <c r="F53" t="n">
-        <v>3.92</v>
+        <v>7.765000000000001</v>
       </c>
       <c r="G53" t="n">
         <v>4.91</v>
       </c>
       <c r="H53" t="n">
-        <v>-0.21</v>
+        <v>2.6975</v>
       </c>
       <c r="I53" t="n">
-        <v>34800</v>
+        <v>18569.5</v>
       </c>
       <c r="J53" t="n">
-        <v>0.02198196673156593</v>
+        <v>1.332812757139437e-20</v>
       </c>
       <c r="K53" t="n">
-        <v>0.471590625</v>
+        <v>0.69825625</v>
       </c>
       <c r="L53" t="inlineStr">
         <is>
-          <t>negligible</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="M53" t="inlineStr"/>
@@ -6888,22 +6824,22 @@
         <v>400</v>
       </c>
       <c r="F54" t="n">
-        <v>3.55</v>
+        <v>5.779999999999999</v>
       </c>
       <c r="G54" t="n">
         <v>4.91</v>
       </c>
       <c r="H54" t="n">
-        <v>-0.9175000000000002</v>
+        <v>1.395</v>
       </c>
       <c r="I54" t="n">
-        <v>23706.5</v>
+        <v>24545.5</v>
       </c>
       <c r="J54" t="n">
-        <v>1.38714509564957e-12</v>
+        <v>1.783747176353621e-11</v>
       </c>
       <c r="K54" t="n">
-        <v>0.382571875</v>
+        <v>0.62699375</v>
       </c>
       <c r="L54" t="inlineStr">
         <is>
@@ -6937,26 +6873,26 @@
         <v>400</v>
       </c>
       <c r="F55" t="n">
-        <v>2.71</v>
+        <v>4.225</v>
       </c>
       <c r="G55" t="n">
         <v>4.91</v>
       </c>
       <c r="H55" t="n">
-        <v>-1.65</v>
+        <v>-0.1549999999999998</v>
       </c>
       <c r="I55" t="n">
-        <v>8837</v>
+        <v>34847</v>
       </c>
       <c r="J55" t="n">
-        <v>1.32904170595827e-41</v>
+        <v>0.023185290731849</v>
       </c>
       <c r="K55" t="n">
-        <v>0.285365625</v>
+        <v>0.5342625</v>
       </c>
       <c r="L55" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>negligible</t>
         </is>
       </c>
       <c r="M55" t="inlineStr"/>
@@ -6986,19 +6922,19 @@
         <v>400</v>
       </c>
       <c r="F56" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="G56" t="n">
         <v>100</v>
       </c>
       <c r="H56" t="n">
-        <v>-97.995</v>
+        <v>-86.39</v>
       </c>
       <c r="I56" t="n">
         <v>0</v>
       </c>
       <c r="J56" t="n">
-        <v>2.412673020165349e-67</v>
+        <v>2.721964412235421e-67</v>
       </c>
       <c r="K56" t="n">
         <v>0</v>
@@ -7035,26 +6971,26 @@
         <v>400</v>
       </c>
       <c r="F57" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="G57" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="H57" t="n">
-        <v>-5.22</v>
+        <v>-85.65000000000001</v>
       </c>
       <c r="I57" t="n">
-        <v>9591</v>
+        <v>0</v>
       </c>
       <c r="J57" t="n">
-        <v>9.766407979267815e-40</v>
+        <v>2.726104985974824e-67</v>
       </c>
       <c r="K57" t="n">
-        <v>0.345</v>
+        <v>0</v>
       </c>
       <c r="L57" t="inlineStr">
         <is>
-          <t>medium</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M57" t="inlineStr"/>
@@ -7084,26 +7020,26 @@
         <v>400</v>
       </c>
       <c r="F58" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="G58" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="H58" t="n">
-        <v>-0.7599999999999998</v>
+        <v>-86.21000000000001</v>
       </c>
       <c r="I58" t="n">
-        <v>20150</v>
+        <v>0</v>
       </c>
       <c r="J58" t="n">
-        <v>6.332733904399474e-18</v>
+        <v>2.725740519675975e-67</v>
       </c>
       <c r="K58" t="n">
-        <v>0.3795875</v>
+        <v>0</v>
       </c>
       <c r="L58" t="inlineStr">
         <is>
-          <t>small</t>
+          <t>large</t>
         </is>
       </c>
       <c r="M58" t="inlineStr"/>
@@ -7133,19 +7069,19 @@
         <v>400</v>
       </c>
       <c r="F59" t="n">
-        <v>2.005</v>
+        <v>13.61</v>
       </c>
       <c r="G59" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H59" t="n">
-        <v>1.72</v>
+        <v>12.075</v>
       </c>
       <c r="I59" t="n">
         <v>0</v>
       </c>
       <c r="J59" t="n">
-        <v>2.669628368671761e-67</v>
+        <v>2.727947235340647e-67</v>
       </c>
       <c r="K59" t="n">
         <v>1</v>
@@ -7182,19 +7118,19 @@
         <v>400</v>
       </c>
       <c r="F60" t="n">
-        <v>2.4</v>
+        <v>14.35</v>
       </c>
       <c r="G60" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H60" t="n">
-        <v>2.105</v>
+        <v>12.625</v>
       </c>
       <c r="I60" t="n">
         <v>0</v>
       </c>
       <c r="J60" t="n">
-        <v>2.661073006956787e-67</v>
+        <v>2.729224096990778e-67</v>
       </c>
       <c r="K60" t="n">
         <v>1</v>
@@ -7231,19 +7167,19 @@
         <v>400</v>
       </c>
       <c r="F61" t="n">
-        <v>2</v>
+        <v>13.79</v>
       </c>
       <c r="G61" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H61" t="n">
-        <v>1.63</v>
+        <v>12.175</v>
       </c>
       <c r="I61" t="n">
         <v>0</v>
       </c>
       <c r="J61" t="n">
-        <v>2.666445086035864e-67</v>
+        <v>2.729396950636073e-67</v>
       </c>
       <c r="K61" t="n">
         <v>1</v>
@@ -7283,16 +7219,16 @@
         <v>100</v>
       </c>
       <c r="G62" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H62" t="n">
-        <v>99.795</v>
+        <v>98.2025</v>
       </c>
       <c r="I62" t="n">
         <v>0</v>
       </c>
       <c r="J62" t="n">
-        <v>6.486318758726508e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K62" t="n">
         <v>1</v>
@@ -7329,19 +7265,19 @@
         <v>400</v>
       </c>
       <c r="F63" t="n">
-        <v>7.56</v>
+        <v>100</v>
       </c>
       <c r="G63" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H63" t="n">
-        <v>7.255</v>
+        <v>98.2025</v>
       </c>
       <c r="I63" t="n">
         <v>0</v>
       </c>
       <c r="J63" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K63" t="n">
         <v>1</v>
@@ -7378,22 +7314,22 @@
         <v>400</v>
       </c>
       <c r="F64" t="n">
-        <v>2.53</v>
+        <v>100</v>
       </c>
       <c r="G64" t="n">
-        <v>0.205</v>
+        <v>1.7975</v>
       </c>
       <c r="H64" t="n">
-        <v>2.33</v>
+        <v>98.2025</v>
       </c>
       <c r="I64" t="n">
         <v>0</v>
       </c>
       <c r="J64" t="n">
-        <v>7.100239880550665e-68</v>
+        <v>2.64538389146274e-67</v>
       </c>
       <c r="K64" t="n">
-        <v>0.99229375</v>
+        <v>1</v>
       </c>
       <c r="L64" t="inlineStr">
         <is>
@@ -7427,22 +7363,22 @@
         <v>416</v>
       </c>
       <c r="F65" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="G65" t="n">
         <v>100</v>
       </c>
       <c r="H65" t="n">
-        <v>-92.45999999999999</v>
+        <v>-90.19</v>
       </c>
       <c r="I65" t="n">
-        <v>2925</v>
+        <v>0</v>
       </c>
       <c r="J65" t="n">
-        <v>2.609313895507326e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K65" t="n">
-        <v>0.1769976192677515</v>
+        <v>0</v>
       </c>
       <c r="L65" t="inlineStr">
         <is>
@@ -7476,22 +7412,22 @@
         <v>416</v>
       </c>
       <c r="F66" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="G66" t="n">
         <v>100</v>
       </c>
       <c r="H66" t="n">
-        <v>-94.19</v>
+        <v>-92.45</v>
       </c>
       <c r="I66" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J66" t="n">
-        <v>2.625471183048989e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K66" t="n">
-        <v>0.1774107803254438</v>
+        <v>0</v>
       </c>
       <c r="L66" t="inlineStr">
         <is>
@@ -7525,22 +7461,22 @@
         <v>416</v>
       </c>
       <c r="F67" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="G67" t="n">
         <v>100</v>
       </c>
       <c r="H67" t="n">
-        <v>-94.19</v>
+        <v>-92.45</v>
       </c>
       <c r="I67" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J67" t="n">
-        <v>2.616561147174345e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K67" t="n">
-        <v>0.1790403106508876</v>
+        <v>0</v>
       </c>
       <c r="L67" t="inlineStr">
         <is>
@@ -7574,22 +7510,22 @@
         <v>416</v>
       </c>
       <c r="F68" t="n">
-        <v>5.57</v>
+        <v>9.81</v>
       </c>
       <c r="G68" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H68" t="n">
-        <v>3.48</v>
+        <v>4.780000000000001</v>
       </c>
       <c r="I68" t="n">
-        <v>117</v>
+        <v>0</v>
       </c>
       <c r="J68" t="n">
-        <v>1.527014197472544e-69</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K68" t="n">
-        <v>0.9134615384615384</v>
+        <v>0.9852648853550295</v>
       </c>
       <c r="L68" t="inlineStr">
         <is>
@@ -7623,22 +7559,22 @@
         <v>416</v>
       </c>
       <c r="F69" t="n">
-        <v>3.65</v>
+        <v>7.55</v>
       </c>
       <c r="G69" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H69" t="n">
-        <v>1.6075</v>
+        <v>2.52</v>
       </c>
       <c r="I69" t="n">
-        <v>4430.5</v>
+        <v>0</v>
       </c>
       <c r="J69" t="n">
-        <v>1.037936694942168e-56</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K69" t="n">
-        <v>0.776702339127219</v>
+        <v>0.7854047244822485</v>
       </c>
       <c r="L69" t="inlineStr">
         <is>
@@ -7672,22 +7608,22 @@
         <v>416</v>
       </c>
       <c r="F70" t="n">
-        <v>3.21</v>
+        <v>7.55</v>
       </c>
       <c r="G70" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H70" t="n">
-        <v>1.185</v>
+        <v>2.52</v>
       </c>
       <c r="I70" t="n">
-        <v>5221</v>
+        <v>0</v>
       </c>
       <c r="J70" t="n">
-        <v>1.669870199611228e-54</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K70" t="n">
-        <v>0.7245198086168639</v>
+        <v>0.7460879715236687</v>
       </c>
       <c r="L70" t="inlineStr">
         <is>
@@ -7724,19 +7660,19 @@
         <v>100</v>
       </c>
       <c r="G71" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H71" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I71" t="n">
-        <v>2800</v>
+        <v>0</v>
       </c>
       <c r="J71" t="n">
-        <v>2.10118130457541e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K71" t="n">
-        <v>0.8505512666420119</v>
+        <v>1</v>
       </c>
       <c r="L71" t="inlineStr">
         <is>
@@ -7773,19 +7709,19 @@
         <v>100</v>
       </c>
       <c r="G72" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H72" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I72" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J72" t="n">
-        <v>4.91990072267415e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K72" t="n">
-        <v>0.8267063840606509</v>
+        <v>1</v>
       </c>
       <c r="L72" t="inlineStr">
         <is>
@@ -7822,19 +7758,19 @@
         <v>100</v>
       </c>
       <c r="G73" t="n">
-        <v>2.7675</v>
+        <v>4.324999999999999</v>
       </c>
       <c r="H73" t="n">
-        <v>96.91500000000001</v>
+        <v>95.675</v>
       </c>
       <c r="I73" t="n">
-        <v>2926</v>
+        <v>0</v>
       </c>
       <c r="J73" t="n">
-        <v>4.919580436851137e-61</v>
+        <v>2.357874314768116e-71</v>
       </c>
       <c r="K73" t="n">
-        <v>0.8216386603180473</v>
+        <v>1</v>
       </c>
       <c r="L73" t="inlineStr">
         <is>
